--- a/autoIt/ImportFiles/TestSmokeSellingRatesImport.xlsx
+++ b/autoIt/ImportFiles/TestSmokeSellingRatesImport.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="242">
   <si>
     <t>ItemName</t>
   </si>
@@ -640,6 +640,111 @@
   </si>
   <si>
     <t>02/01/2023</t>
+  </si>
+  <si>
+    <t>23/01/2023</t>
+  </si>
+  <si>
+    <t>31/01/2023</t>
+  </si>
+  <si>
+    <t>02/02/2023</t>
+  </si>
+  <si>
+    <t>07/02/2023</t>
+  </si>
+  <si>
+    <t>08/02/2023</t>
+  </si>
+  <si>
+    <t>13/02/2023</t>
+  </si>
+  <si>
+    <t>09/02/2023</t>
+  </si>
+  <si>
+    <t>14/02/2023</t>
+  </si>
+  <si>
+    <t>10/02/2023</t>
+  </si>
+  <si>
+    <t>19/02/2023</t>
+  </si>
+  <si>
+    <t>17/02/2023</t>
+  </si>
+  <si>
+    <t>22/02/2023</t>
+  </si>
+  <si>
+    <t>20/02/2023</t>
+  </si>
+  <si>
+    <t>21/02/2023</t>
+  </si>
+  <si>
+    <t>26/02/2023</t>
+  </si>
+  <si>
+    <t>27/02/2023</t>
+  </si>
+  <si>
+    <t>04/03/2023</t>
+  </si>
+  <si>
+    <t>01/03/2023</t>
+  </si>
+  <si>
+    <t>05/03/2023</t>
+  </si>
+  <si>
+    <t>10/03/2023</t>
+  </si>
+  <si>
+    <t>06/03/2023</t>
+  </si>
+  <si>
+    <t>11/03/2023</t>
+  </si>
+  <si>
+    <t>08/03/2023</t>
+  </si>
+  <si>
+    <t>09/03/2023</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>13/03/2023</t>
+  </si>
+  <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
+    <t>12/04/2023</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
+    <t>06/05/2023</t>
+  </si>
+  <si>
+    <t>11/05/2023</t>
+  </si>
+  <si>
+    <t>10/05/2023</t>
+  </si>
+  <si>
+    <t>15/05/2023</t>
   </si>
 </sst>
 </file>
@@ -1058,13 +1163,13 @@
         <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="G2" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>28</v>
@@ -1129,13 +1234,13 @@
         <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="G3" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>28</v>
